--- a/Full_First_Sec_Analysis_Handicaps_CorrectScores.xlsx
+++ b/Full_First_Sec_Analysis_Handicaps_CorrectScores.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IQ82"/>
+  <dimension ref="A1:IR82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1687,6 +1687,11 @@
           <t>2H_HomeOrAway</t>
         </is>
       </c>
+      <c r="IR1" s="1" t="inlineStr">
+        <is>
+          <t>Multigoal1st2ndfullDC</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2452,6 +2457,9 @@
       <c r="IQ2" t="n">
         <v>1</v>
       </c>
+      <c r="IR2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3217,6 +3225,9 @@
       <c r="IQ3" t="n">
         <v>1</v>
       </c>
+      <c r="IR3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3982,6 +3993,9 @@
       <c r="IQ4" t="n">
         <v>1</v>
       </c>
+      <c r="IR4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4747,6 +4761,9 @@
       <c r="IQ5" t="n">
         <v>0</v>
       </c>
+      <c r="IR5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5512,6 +5529,9 @@
       <c r="IQ6" t="n">
         <v>1</v>
       </c>
+      <c r="IR6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6277,6 +6297,9 @@
       <c r="IQ7" t="n">
         <v>1</v>
       </c>
+      <c r="IR7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7042,6 +7065,9 @@
       <c r="IQ8" t="n">
         <v>1</v>
       </c>
+      <c r="IR8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7807,6 +7833,9 @@
       <c r="IQ9" t="n">
         <v>1</v>
       </c>
+      <c r="IR9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8572,6 +8601,9 @@
       <c r="IQ10" t="n">
         <v>0</v>
       </c>
+      <c r="IR10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9337,6 +9369,9 @@
       <c r="IQ11" t="n">
         <v>1</v>
       </c>
+      <c r="IR11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10102,6 +10137,9 @@
       <c r="IQ12" t="n">
         <v>1</v>
       </c>
+      <c r="IR12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10867,6 +10905,9 @@
       <c r="IQ13" t="n">
         <v>1</v>
       </c>
+      <c r="IR13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11632,6 +11673,9 @@
       <c r="IQ14" t="n">
         <v>1</v>
       </c>
+      <c r="IR14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12397,6 +12441,9 @@
       <c r="IQ15" t="n">
         <v>1</v>
       </c>
+      <c r="IR15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13162,6 +13209,9 @@
       <c r="IQ16" t="n">
         <v>1</v>
       </c>
+      <c r="IR16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13927,6 +13977,9 @@
       <c r="IQ17" t="n">
         <v>1</v>
       </c>
+      <c r="IR17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14692,6 +14745,9 @@
       <c r="IQ18" t="n">
         <v>1</v>
       </c>
+      <c r="IR18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -15457,6 +15513,9 @@
       <c r="IQ19" t="n">
         <v>0</v>
       </c>
+      <c r="IR19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -16222,6 +16281,9 @@
       <c r="IQ20" t="n">
         <v>1</v>
       </c>
+      <c r="IR20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -16987,6 +17049,9 @@
       <c r="IQ21" t="n">
         <v>0</v>
       </c>
+      <c r="IR21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -17752,6 +17817,9 @@
       <c r="IQ22" t="n">
         <v>1</v>
       </c>
+      <c r="IR22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -18517,6 +18585,9 @@
       <c r="IQ23" t="n">
         <v>1</v>
       </c>
+      <c r="IR23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -19282,6 +19353,9 @@
       <c r="IQ24" t="n">
         <v>0</v>
       </c>
+      <c r="IR24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -20047,6 +20121,9 @@
       <c r="IQ25" t="n">
         <v>1</v>
       </c>
+      <c r="IR25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -20812,6 +20889,9 @@
       <c r="IQ26" t="n">
         <v>0</v>
       </c>
+      <c r="IR26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -21577,6 +21657,9 @@
       <c r="IQ27" t="n">
         <v>1</v>
       </c>
+      <c r="IR27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -22342,6 +22425,9 @@
       <c r="IQ28" t="n">
         <v>0</v>
       </c>
+      <c r="IR28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -23107,6 +23193,9 @@
       <c r="IQ29" t="n">
         <v>0</v>
       </c>
+      <c r="IR29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -23872,6 +23961,9 @@
       <c r="IQ30" t="n">
         <v>0</v>
       </c>
+      <c r="IR30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -24637,6 +24729,9 @@
       <c r="IQ31" t="n">
         <v>0</v>
       </c>
+      <c r="IR31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -25402,6 +25497,9 @@
       <c r="IQ32" t="n">
         <v>1</v>
       </c>
+      <c r="IR32" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -26167,6 +26265,9 @@
       <c r="IQ33" t="n">
         <v>0</v>
       </c>
+      <c r="IR33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -26932,6 +27033,9 @@
       <c r="IQ34" t="n">
         <v>1</v>
       </c>
+      <c r="IR34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -27697,6 +27801,9 @@
       <c r="IQ35" t="n">
         <v>1</v>
       </c>
+      <c r="IR35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -28462,6 +28569,9 @@
       <c r="IQ36" t="n">
         <v>1</v>
       </c>
+      <c r="IR36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -29227,6 +29337,9 @@
       <c r="IQ37" t="n">
         <v>1</v>
       </c>
+      <c r="IR37" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -29992,6 +30105,9 @@
       <c r="IQ38" t="n">
         <v>1</v>
       </c>
+      <c r="IR38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -30757,6 +30873,9 @@
       <c r="IQ39" t="n">
         <v>1</v>
       </c>
+      <c r="IR39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -31522,6 +31641,9 @@
       <c r="IQ40" t="n">
         <v>1</v>
       </c>
+      <c r="IR40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -32287,6 +32409,9 @@
       <c r="IQ41" t="n">
         <v>0</v>
       </c>
+      <c r="IR41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -33052,6 +33177,9 @@
       <c r="IQ42" t="n">
         <v>0</v>
       </c>
+      <c r="IR42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -33817,6 +33945,9 @@
       <c r="IQ43" t="n">
         <v>0</v>
       </c>
+      <c r="IR43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -34582,6 +34713,9 @@
       <c r="IQ44" t="n">
         <v>0</v>
       </c>
+      <c r="IR44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -35347,6 +35481,9 @@
       <c r="IQ45" t="n">
         <v>0</v>
       </c>
+      <c r="IR45" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -36112,6 +36249,9 @@
       <c r="IQ46" t="n">
         <v>1</v>
       </c>
+      <c r="IR46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -36877,6 +37017,9 @@
       <c r="IQ47" t="n">
         <v>0</v>
       </c>
+      <c r="IR47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -37642,6 +37785,9 @@
       <c r="IQ48" t="n">
         <v>1</v>
       </c>
+      <c r="IR48" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -38407,6 +38553,9 @@
       <c r="IQ49" t="n">
         <v>1</v>
       </c>
+      <c r="IR49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -39172,6 +39321,9 @@
       <c r="IQ50" t="n">
         <v>1</v>
       </c>
+      <c r="IR50" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -39937,6 +40089,9 @@
       <c r="IQ51" t="n">
         <v>1</v>
       </c>
+      <c r="IR51" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -40702,6 +40857,9 @@
       <c r="IQ52" t="n">
         <v>1</v>
       </c>
+      <c r="IR52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -41467,6 +41625,9 @@
       <c r="IQ53" t="n">
         <v>0</v>
       </c>
+      <c r="IR53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -42232,6 +42393,9 @@
       <c r="IQ54" t="n">
         <v>0</v>
       </c>
+      <c r="IR54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -42997,6 +43161,9 @@
       <c r="IQ55" t="n">
         <v>0</v>
       </c>
+      <c r="IR55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -43762,6 +43929,9 @@
       <c r="IQ56" t="n">
         <v>0</v>
       </c>
+      <c r="IR56" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -44527,6 +44697,9 @@
       <c r="IQ57" t="n">
         <v>0</v>
       </c>
+      <c r="IR57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -45292,6 +45465,9 @@
       <c r="IQ58" t="n">
         <v>0</v>
       </c>
+      <c r="IR58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -46057,6 +46233,9 @@
       <c r="IQ59" t="n">
         <v>1</v>
       </c>
+      <c r="IR59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -46822,6 +47001,9 @@
       <c r="IQ60" t="n">
         <v>0</v>
       </c>
+      <c r="IR60" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -47587,6 +47769,9 @@
       <c r="IQ61" t="n">
         <v>1</v>
       </c>
+      <c r="IR61" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -48352,6 +48537,9 @@
       <c r="IQ62" t="n">
         <v>1</v>
       </c>
+      <c r="IR62" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -49117,6 +49305,9 @@
       <c r="IQ63" t="n">
         <v>1</v>
       </c>
+      <c r="IR63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -49882,6 +50073,9 @@
       <c r="IQ64" t="n">
         <v>1</v>
       </c>
+      <c r="IR64" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -50647,6 +50841,9 @@
       <c r="IQ65" t="n">
         <v>1</v>
       </c>
+      <c r="IR65" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -51412,6 +51609,9 @@
       <c r="IQ66" t="n">
         <v>1</v>
       </c>
+      <c r="IR66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -52177,6 +52377,9 @@
       <c r="IQ67" t="n">
         <v>1</v>
       </c>
+      <c r="IR67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -52942,6 +53145,9 @@
       <c r="IQ68" t="n">
         <v>1</v>
       </c>
+      <c r="IR68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -53707,6 +53913,9 @@
       <c r="IQ69" t="n">
         <v>1</v>
       </c>
+      <c r="IR69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -54472,6 +54681,9 @@
       <c r="IQ70" t="n">
         <v>1</v>
       </c>
+      <c r="IR70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -55237,6 +55449,9 @@
       <c r="IQ71" t="n">
         <v>0</v>
       </c>
+      <c r="IR71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -56002,6 +56217,9 @@
       <c r="IQ72" t="n">
         <v>0</v>
       </c>
+      <c r="IR72" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -56767,6 +56985,9 @@
       <c r="IQ73" t="n">
         <v>1</v>
       </c>
+      <c r="IR73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -57532,6 +57753,9 @@
       <c r="IQ74" t="n">
         <v>0</v>
       </c>
+      <c r="IR74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -58297,6 +58521,9 @@
       <c r="IQ75" t="n">
         <v>0</v>
       </c>
+      <c r="IR75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -59062,6 +59289,9 @@
       <c r="IQ76" t="n">
         <v>1</v>
       </c>
+      <c r="IR76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -59827,6 +60057,9 @@
       <c r="IQ77" t="n">
         <v>1</v>
       </c>
+      <c r="IR77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -60592,6 +60825,9 @@
       <c r="IQ78" t="n">
         <v>1</v>
       </c>
+      <c r="IR78" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -61357,6 +61593,9 @@
       <c r="IQ79" t="n">
         <v>1</v>
       </c>
+      <c r="IR79" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -62122,6 +62361,9 @@
       <c r="IQ80" t="n">
         <v>0</v>
       </c>
+      <c r="IR80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -62887,6 +63129,9 @@
       <c r="IQ81" t="n">
         <v>1</v>
       </c>
+      <c r="IR81" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -63651,6 +63896,9 @@
       </c>
       <c r="IQ82" t="n">
         <v>1</v>
+      </c>
+      <c r="IR82" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -63664,7 +63912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IM10"/>
+  <dimension ref="A1:IN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64903,6 +65151,11 @@
           <t>2H_HomeOrAway</t>
         </is>
       </c>
+      <c r="IN1" s="1" t="inlineStr">
+        <is>
+          <t>Multigoal1st2ndfullDC</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -65648,6 +65901,9 @@
       <c r="IM2" t="n">
         <v>8</v>
       </c>
+      <c r="IN2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -66393,6 +66649,9 @@
       <c r="IM3" t="n">
         <v>8</v>
       </c>
+      <c r="IN3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -67138,6 +67397,9 @@
       <c r="IM4" t="n">
         <v>4</v>
       </c>
+      <c r="IN4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -67883,6 +68145,9 @@
       <c r="IM5" t="n">
         <v>4</v>
       </c>
+      <c r="IN5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -68628,6 +68893,9 @@
       <c r="IM6" t="n">
         <v>5</v>
       </c>
+      <c r="IN6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -69373,6 +69641,9 @@
       <c r="IM7" t="n">
         <v>5</v>
       </c>
+      <c r="IN7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -70118,6 +70389,9 @@
       <c r="IM8" t="n">
         <v>5</v>
       </c>
+      <c r="IN8" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -70863,6 +71137,9 @@
       <c r="IM9" t="n">
         <v>7</v>
       </c>
+      <c r="IN9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -71607,6 +71884,9 @@
       </c>
       <c r="IM10" t="n">
         <v>6</v>
+      </c>
+      <c r="IN10" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -71620,7 +71900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IM19"/>
+  <dimension ref="A1:IN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72859,6 +73139,11 @@
           <t>2H_HomeOrAway</t>
         </is>
       </c>
+      <c r="IN1" s="1" t="inlineStr">
+        <is>
+          <t>Multigoal1st2ndfullDC</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -73604,6 +73889,9 @@
       <c r="IM2" t="n">
         <v>4</v>
       </c>
+      <c r="IN2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -74349,6 +74637,9 @@
       <c r="IM3" t="n">
         <v>3</v>
       </c>
+      <c r="IN3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -75094,6 +75385,9 @@
       <c r="IM4" t="n">
         <v>3</v>
       </c>
+      <c r="IN4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -75839,6 +76133,9 @@
       <c r="IM5" t="n">
         <v>3</v>
       </c>
+      <c r="IN5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -76584,6 +76881,9 @@
       <c r="IM6" t="n">
         <v>2</v>
       </c>
+      <c r="IN6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -77329,6 +77629,9 @@
       <c r="IM7" t="n">
         <v>3</v>
       </c>
+      <c r="IN7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -78074,6 +78377,9 @@
       <c r="IM8" t="n">
         <v>3</v>
       </c>
+      <c r="IN8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -78819,6 +79125,9 @@
       <c r="IM9" t="n">
         <v>3</v>
       </c>
+      <c r="IN9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -79564,6 +79873,9 @@
       <c r="IM10" t="n">
         <v>2</v>
       </c>
+      <c r="IN10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -80309,6 +80621,9 @@
       <c r="IM11" t="n">
         <v>3</v>
       </c>
+      <c r="IN11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -81054,6 +81369,9 @@
       <c r="IM12" t="n">
         <v>1</v>
       </c>
+      <c r="IN12" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -81799,6 +82117,9 @@
       <c r="IM13" t="n">
         <v>3</v>
       </c>
+      <c r="IN13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -82544,6 +82865,9 @@
       <c r="IM14" t="n">
         <v>2</v>
       </c>
+      <c r="IN14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -83289,6 +83613,9 @@
       <c r="IM15" t="n">
         <v>5</v>
       </c>
+      <c r="IN15" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -84034,6 +84361,9 @@
       <c r="IM16" t="n">
         <v>4</v>
       </c>
+      <c r="IN16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -84779,6 +85109,9 @@
       <c r="IM17" t="n">
         <v>2</v>
       </c>
+      <c r="IN17" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -85524,6 +85857,9 @@
       <c r="IM18" t="n">
         <v>3</v>
       </c>
+      <c r="IN18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -86268,6 +86604,9 @@
       </c>
       <c r="IM19" t="n">
         <v>3</v>
+      </c>
+      <c r="IN19" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -86281,7 +86620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IM19"/>
+  <dimension ref="A1:IN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87520,6 +87859,11 @@
           <t>2H_HomeOrAway</t>
         </is>
       </c>
+      <c r="IN1" s="1" t="inlineStr">
+        <is>
+          <t>Multigoal1st2ndfullDC</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -88265,6 +88609,9 @@
       <c r="IM2" t="n">
         <v>3</v>
       </c>
+      <c r="IN2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -89010,6 +89357,9 @@
       <c r="IM3" t="n">
         <v>3</v>
       </c>
+      <c r="IN3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -89755,6 +90105,9 @@
       <c r="IM4" t="n">
         <v>3</v>
       </c>
+      <c r="IN4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -90500,6 +90853,9 @@
       <c r="IM5" t="n">
         <v>4</v>
       </c>
+      <c r="IN5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -91245,6 +91601,9 @@
       <c r="IM6" t="n">
         <v>1</v>
       </c>
+      <c r="IN6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -91990,6 +92349,9 @@
       <c r="IM7" t="n">
         <v>3</v>
       </c>
+      <c r="IN7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -92735,6 +93097,9 @@
       <c r="IM8" t="n">
         <v>2</v>
       </c>
+      <c r="IN8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -93480,6 +93845,9 @@
       <c r="IM9" t="n">
         <v>3</v>
       </c>
+      <c r="IN9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -94225,6 +94593,9 @@
       <c r="IM10" t="n">
         <v>2</v>
       </c>
+      <c r="IN10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -94970,6 +95341,9 @@
       <c r="IM11" t="n">
         <v>2</v>
       </c>
+      <c r="IN11" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -95715,6 +96089,9 @@
       <c r="IM12" t="n">
         <v>3</v>
       </c>
+      <c r="IN12" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -96460,6 +96837,9 @@
       <c r="IM13" t="n">
         <v>4</v>
       </c>
+      <c r="IN13" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -97205,6 +97585,9 @@
       <c r="IM14" t="n">
         <v>2</v>
       </c>
+      <c r="IN14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -97950,6 +98333,9 @@
       <c r="IM15" t="n">
         <v>3</v>
       </c>
+      <c r="IN15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -98695,6 +99081,9 @@
       <c r="IM16" t="n">
         <v>5</v>
       </c>
+      <c r="IN16" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -99440,6 +99829,9 @@
       <c r="IM17" t="n">
         <v>3</v>
       </c>
+      <c r="IN17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -100185,6 +100577,9 @@
       <c r="IM18" t="n">
         <v>4</v>
       </c>
+      <c r="IN18" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -100928,6 +101323,9 @@
         <v>3</v>
       </c>
       <c r="IM19" t="n">
+        <v>2</v>
+      </c>
+      <c r="IN19" t="n">
         <v>2</v>
       </c>
     </row>
